--- a/artfynd/A 8987-2026 artfynd.xlsx
+++ b/artfynd/A 8987-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131431006</v>
       </c>
       <c r="B2" t="n">
-        <v>106143</v>
+        <v>106144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>131431028</v>
       </c>
       <c r="B4" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131431434</v>
       </c>
       <c r="B5" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131431507</v>
       </c>
       <c r="B6" t="n">
-        <v>99022</v>
+        <v>99023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8987-2026 artfynd.xlsx
+++ b/artfynd/A 8987-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131431006</v>
       </c>
       <c r="B2" t="n">
-        <v>106144</v>
+        <v>106148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131430947</v>
       </c>
       <c r="B3" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>131431028</v>
       </c>
       <c r="B4" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131431434</v>
       </c>
       <c r="B5" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131431507</v>
       </c>
       <c r="B6" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8987-2026 artfynd.xlsx
+++ b/artfynd/A 8987-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131431006</v>
       </c>
       <c r="B2" t="n">
-        <v>106148</v>
+        <v>106153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131430947</v>
       </c>
       <c r="B3" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>131431028</v>
       </c>
       <c r="B4" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131431434</v>
       </c>
       <c r="B5" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131431507</v>
       </c>
       <c r="B6" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8987-2026 artfynd.xlsx
+++ b/artfynd/A 8987-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131431006</v>
       </c>
       <c r="B2" t="n">
-        <v>106153</v>
+        <v>106159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131430947</v>
       </c>
       <c r="B3" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>131431028</v>
       </c>
       <c r="B4" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131431434</v>
       </c>
       <c r="B5" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131431507</v>
       </c>
       <c r="B6" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8987-2026 artfynd.xlsx
+++ b/artfynd/A 8987-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131431006</v>
       </c>
       <c r="B2" t="n">
-        <v>106159</v>
+        <v>106160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>131431028</v>
       </c>
       <c r="B4" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131431434</v>
       </c>
       <c r="B5" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131431507</v>
       </c>
       <c r="B6" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8987-2026 artfynd.xlsx
+++ b/artfynd/A 8987-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131431006</v>
       </c>
       <c r="B2" t="n">
-        <v>106160</v>
+        <v>106161</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131430947</v>
       </c>
       <c r="B3" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>131431028</v>
       </c>
       <c r="B4" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131431434</v>
       </c>
       <c r="B5" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131431507</v>
       </c>
       <c r="B6" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8987-2026 artfynd.xlsx
+++ b/artfynd/A 8987-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131431006</v>
       </c>
       <c r="B2" t="n">
-        <v>106161</v>
+        <v>106159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131430947</v>
       </c>
       <c r="B3" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>131431028</v>
       </c>
       <c r="B4" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>131431434</v>
       </c>
       <c r="B5" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>131431507</v>
       </c>
       <c r="B6" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8987-2026 artfynd.xlsx
+++ b/artfynd/A 8987-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131431006</v>
       </c>
       <c r="B2" t="n">
-        <v>106159</v>
+        <v>106160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
